--- a/Experiment 3 - SOS vs Random Mutation/Spon_SOS_Cleaned_Estimate.xlsx
+++ b/Experiment 3 - SOS vs Random Mutation/Spon_SOS_Cleaned_Estimate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E2" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -487,10 +487,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>11287</v>
+        <v>21931</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -498,24 +498,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E3" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>9.331406899955626</v>
+        <v>9.995656440007505</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>21931</v>
+        <v>19650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -523,24 +523,24 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E4" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>9.995656440007505</v>
+        <v>9.885832617297407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>19650</v>
+        <v>26696</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -548,24 +548,24 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E5" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>9.885832617297407</v>
+        <v>10.19226902043121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>26696</v>
+        <v>17714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -573,24 +573,24 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E6" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>10.19226902043121</v>
+        <v>9.782110566369528</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>17714</v>
+        <v>25094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E7" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>9.782110566369528</v>
+        <v>10.13038405271964</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>25094</v>
+        <v>28007</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -623,24 +623,24 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E8" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>10.13038405271964</v>
+        <v>10.24020975791255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>28007</v>
+        <v>18679</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -648,24 +648,24 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E9" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>10.24020975791255</v>
+        <v>9.835155177159303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>18679</v>
+        <v>19643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -673,24 +673,24 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E10" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>9.835155177159303</v>
+        <v>9.885476319734277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>19643</v>
+        <v>19232</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -698,24 +698,24 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E11" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>9.885476319734277</v>
+        <v>9.864330837334935</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>19232</v>
+        <v>21931</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -723,24 +723,24 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E12" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>9.864330837334935</v>
+        <v>9.995656440007505</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>11287</v>
+        <v>19650</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -748,24 +748,24 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E13" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>9.331406899955626</v>
+        <v>9.885832617297407</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>21931</v>
+        <v>26696</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -773,24 +773,24 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E14" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>9.995656440007505</v>
+        <v>10.19226902043121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>19650</v>
+        <v>17714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -798,24 +798,24 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E15" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>9.885832617297407</v>
+        <v>9.782110566369528</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" t="n">
-        <v>26696</v>
+        <v>25094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -823,24 +823,24 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E16" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>10.19226902043121</v>
+        <v>10.13038405271964</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" t="n">
-        <v>17714</v>
+        <v>28007</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -848,24 +848,24 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E17" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>9.782110566369528</v>
+        <v>10.24020975791255</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>25094</v>
+        <v>18679</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -873,24 +873,24 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E18" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>10.13038405271964</v>
+        <v>9.835155177159303</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" t="n">
-        <v>28007</v>
+        <v>19643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -898,24 +898,24 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E19" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>10.24020975791255</v>
+        <v>9.885476319734277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>18679</v>
+        <v>21265</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -923,24 +923,24 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E20" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>9.835155177159303</v>
+        <v>9.964817807687734</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" t="n">
-        <v>19643</v>
+        <v>21377</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -948,24 +948,24 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E21" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>9.885476319734277</v>
+        <v>9.97007085667928</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" t="n">
-        <v>21265</v>
+        <v>22322</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -973,24 +973,24 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E22" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>9.964817807687734</v>
+        <v>10.01332801821566</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" t="n">
-        <v>21377</v>
+        <v>24275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -998,24 +998,24 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E23" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>9.97007085667928</v>
+        <v>10.09720229315953</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" t="n">
-        <v>22322</v>
+        <v>30816</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1023,24 +1023,24 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E24" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>10.01332801821566</v>
+        <v>10.33578931459785</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" t="n">
-        <v>24275</v>
+        <v>16545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1048,24 +1048,24 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E25" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>10.09720229315953</v>
+        <v>9.713839220355712</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" t="n">
-        <v>30816</v>
+        <v>19903</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1073,24 +1073,24 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E26" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>10.33578931459785</v>
+        <v>9.898625753119221</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>16545</v>
+        <v>21530</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1098,24 +1098,24 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E27" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>9.713839220355712</v>
+        <v>9.977202590358409</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>19903</v>
+        <v>21976</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1123,24 +1123,24 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E28" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>9.898625753119221</v>
+        <v>9.99770622777511</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>39176</v>
+        <v>24713</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1148,24 +1148,24 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E29" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>10.57581959338215</v>
+        <v>10.11508469994997</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>21530</v>
+        <v>23243</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1173,24 +1173,24 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E30" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>9.977202590358409</v>
+        <v>10.05375929041443</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>21976</v>
+        <v>21561</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1198,24 +1198,24 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E31" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>9.99770622777511</v>
+        <v>9.978641406136552</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>24713</v>
+        <v>21740</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1223,24 +1223,24 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E32" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>10.11508469994997</v>
+        <v>9.9869091606752</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>23243</v>
+        <v>18463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1248,24 +1248,24 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E33" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>10.05375929041443</v>
+        <v>9.823524008395744</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>21561</v>
+        <v>17179</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1273,24 +1273,24 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E34" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>9.978641406136552</v>
+        <v>9.751442986626445</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>21740</v>
+        <v>24412</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1298,24 +1298,24 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E35" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>9.9869091606752</v>
+        <v>10.10283009366439</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>18463</v>
+        <v>26431</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1323,24 +1323,24 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E36" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>9.823524008395744</v>
+        <v>10.18229284267524</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>17179</v>
+        <v>23323</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1348,24 +1348,24 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E37" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>9.751442986626445</v>
+        <v>10.05719527713034</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>24412</v>
+        <v>26872</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1373,24 +1373,24 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E38" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>10.10283009366439</v>
+        <v>10.19884013129213</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>26431</v>
+        <v>19027</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1398,24 +1398,24 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E39" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>10.18229284267524</v>
+        <v>9.8536143020404</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>23323</v>
+        <v>28879</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1423,24 +1423,24 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E40" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>10.05719527713034</v>
+        <v>10.27086996636849</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>26872</v>
+        <v>18884</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1448,24 +1448,24 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E41" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>10.19884013129213</v>
+        <v>9.846070281666178</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>19027</v>
+        <v>20187</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1473,24 +1473,24 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E42" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>9.8536143020404</v>
+        <v>9.912794111856428</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n">
-        <v>28879</v>
+        <v>21322</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1498,24 +1498,24 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E43" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>10.27086996636849</v>
+        <v>9.96749468251042</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n">
-        <v>18884</v>
+        <v>26316</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1523,24 +1523,24 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E44" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>9.846070281666178</v>
+        <v>10.17793239820589</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n">
-        <v>20187</v>
+        <v>19711</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1548,24 +1548,24 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E45" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>9.912794111856428</v>
+        <v>9.888932134526929</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n">
-        <v>36209</v>
+        <v>24521</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1573,24 +1573,24 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E46" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>10.49706298569786</v>
+        <v>10.1072851722528</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n">
-        <v>21322</v>
+        <v>28146</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1598,24 +1598,24 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E47" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>9.96749468251042</v>
+        <v>10.24516052755651</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n">
-        <v>26316</v>
+        <v>18798</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1623,24 +1623,24 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E48" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>10.17793239820589</v>
+        <v>9.841505760180247</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n">
-        <v>19711</v>
+        <v>28569</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1648,24 +1648,24 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E49" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>9.888932134526929</v>
+        <v>10.26007749286216</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n">
-        <v>24521</v>
+        <v>25077</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1673,24 +1673,24 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E50" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>10.1072851722528</v>
+        <v>10.12970637036727</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n">
-        <v>28146</v>
+        <v>29094</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1698,24 +1698,24 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E51" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>10.24516052755651</v>
+        <v>10.27828724633341</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n">
-        <v>18798</v>
+        <v>24085</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1723,24 +1723,24 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E52" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>9.841505760180247</v>
+        <v>10.08934451906432</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n">
-        <v>28569</v>
+        <v>19852</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1748,24 +1748,24 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E53" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>10.26007749286216</v>
+        <v>9.896060036707331</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n">
-        <v>25077</v>
+        <v>21048</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1773,24 +1773,24 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E54" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>10.12970637036727</v>
+        <v>9.954560822720129</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n">
-        <v>29094</v>
+        <v>17948</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1798,24 +1798,24 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E55" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>10.27828724633341</v>
+        <v>9.795233967095873</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n">
-        <v>24085</v>
+        <v>16730</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1823,24 +1823,24 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E56" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>10.08934451906432</v>
+        <v>9.724958793980869</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n">
-        <v>19852</v>
+        <v>22241</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1848,24 +1848,24 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E57" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>9.896060036707331</v>
+        <v>10.00969271138244</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n">
-        <v>21048</v>
+        <v>12174</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1873,24 +1873,24 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E58" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>9.954560822720129</v>
+        <v>9.407057809053869</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n">
-        <v>17948</v>
+        <v>28310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1898,24 +1898,24 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E59" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>9.795233967095873</v>
+        <v>10.25097037810595</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n">
-        <v>16730</v>
+        <v>19955</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1923,24 +1923,24 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E60" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>9.724958793980869</v>
+        <v>9.901235017482835</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n">
-        <v>22241</v>
+        <v>22235</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1948,24 +1948,24 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E61" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>10.00969271138244</v>
+        <v>10.0094229029448</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n">
-        <v>12174</v>
+        <v>18482</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1973,24 +1973,24 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E62" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>9.407057809053869</v>
+        <v>9.824552564447986</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n">
-        <v>28310</v>
+        <v>16728</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1998,24 +1998,24 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E63" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>10.25097037810595</v>
+        <v>9.724839241108469</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n">
-        <v>19955</v>
+        <v>13341</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2023,24 +2023,24 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E64" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>9.901235017482835</v>
+        <v>9.498597279178806</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n">
-        <v>22235</v>
+        <v>20871</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2048,24 +2048,24 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E65" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>10.0094229029448</v>
+        <v>9.946115914591751</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n">
-        <v>18482</v>
+        <v>29148</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2073,24 +2073,24 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E66" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>9.824552564447986</v>
+        <v>10.28014157879017</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n">
-        <v>16728</v>
+        <v>19996</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2098,24 +2098,24 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E67" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>9.724839241108469</v>
+        <v>9.903287532533462</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n">
-        <v>13341</v>
+        <v>21397</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2123,24 +2123,24 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E68" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>9.498597279178806</v>
+        <v>9.97100600426695</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n">
-        <v>20871</v>
+        <v>19346</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2148,24 +2148,24 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E69" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>9.946115914591751</v>
+        <v>9.870240958742492</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n">
-        <v>29148</v>
+        <v>24691</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2173,24 +2173,24 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E70" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>10.28014157879017</v>
+        <v>10.11419408374666</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n">
-        <v>19996</v>
+        <v>20727</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2198,24 +2198,24 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E71" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>9.903287532533462</v>
+        <v>9.939192477156904</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n">
-        <v>21397</v>
+        <v>19232</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E72" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>9.97100600426695</v>
+        <v>9.864330837334935</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n">
-        <v>19346</v>
+        <v>21931</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2248,24 +2248,24 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E73" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>9.870240958742492</v>
+        <v>9.995656440007505</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n">
-        <v>24691</v>
+        <v>19650</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2273,24 +2273,24 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E74" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>10.11419408374666</v>
+        <v>9.885832617297407</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n">
-        <v>20727</v>
+        <v>26696</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2298,24 +2298,24 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E75" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>9.939192477156904</v>
+        <v>10.19226902043121</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n">
-        <v>19232</v>
+        <v>17714</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2323,24 +2323,24 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E76" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>9.864330837334935</v>
+        <v>9.782110566369528</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n">
-        <v>11287</v>
+        <v>19232</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E77" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>9.331406899955626</v>
+        <v>9.864330837334935</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B78" t="n">
         <v>21931</v>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E78" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B79" t="n">
         <v>19650</v>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E79" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B80" t="n">
-        <v>26696</v>
+        <v>17714</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2423,24 +2423,24 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E80" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>10.19226902043121</v>
+        <v>9.782110566369528</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B81" t="n">
-        <v>17714</v>
+        <v>25094</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2448,24 +2448,24 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E81" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>9.782110566369528</v>
+        <v>10.13038405271964</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B82" t="n">
-        <v>19232</v>
+        <v>28007</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2473,24 +2473,24 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E82" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>9.864330837334935</v>
+        <v>10.24020975791255</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B83" t="n">
-        <v>11287</v>
+        <v>18679</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2498,24 +2498,24 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E83" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>9.331406899955626</v>
+        <v>9.835155177159303</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B84" t="n">
-        <v>21931</v>
+        <v>19643</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2523,24 +2523,24 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E84" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>9.995656440007505</v>
+        <v>9.885476319734277</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B85" t="n">
-        <v>19650</v>
+        <v>21265</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2548,24 +2548,24 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E85" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>9.885832617297407</v>
+        <v>9.964817807687734</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B86" t="n">
-        <v>17714</v>
+        <v>21377</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2573,24 +2573,24 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E86" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>9.782110566369528</v>
+        <v>9.97007085667928</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B87" t="n">
-        <v>25094</v>
+        <v>22322</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2598,24 +2598,24 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E87" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>10.13038405271964</v>
+        <v>10.01332801821566</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B88" t="n">
-        <v>28007</v>
+        <v>16545</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2623,24 +2623,24 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E88" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>10.24020975791255</v>
+        <v>9.713839220355712</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B89" t="n">
-        <v>18679</v>
+        <v>19903</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2648,24 +2648,24 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E89" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>9.835155177159303</v>
+        <v>9.898625753119221</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B90" t="n">
-        <v>19643</v>
+        <v>21530</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2673,24 +2673,24 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E90" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>9.885476319734277</v>
+        <v>9.977202590358409</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B91" t="n">
-        <v>21265</v>
+        <v>21976</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2698,24 +2698,24 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E91" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>9.964817807687734</v>
+        <v>9.99770622777511</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B92" t="n">
-        <v>21377</v>
+        <v>23243</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2723,24 +2723,24 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E92" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>9.97007085667928</v>
+        <v>10.05375929041443</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B93" t="n">
-        <v>22322</v>
+        <v>21561</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2748,24 +2748,24 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E93" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>10.01332801821566</v>
+        <v>9.978641406136552</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B94" t="n">
-        <v>16545</v>
+        <v>21740</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2773,24 +2773,24 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E94" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>9.713839220355712</v>
+        <v>9.9869091606752</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B95" t="n">
-        <v>19903</v>
+        <v>18463</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2798,174 +2798,174 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>4.608176226510968</v>
+        <v>6.212791350191666</v>
       </c>
       <c r="E95" t="n">
-        <v>23531.91614294722</v>
+        <v>23323.52071853251</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>9.898625753119221</v>
+        <v>9.823524008395744</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B96" t="n">
-        <v>21530</v>
+        <v>26374</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>Spontaneous</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4.608176226510968</v>
+        <v>2.968933156507309</v>
       </c>
       <c r="E96" t="n">
-        <v>23531.91614294722</v>
+        <v>69444.47043386118</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>9.977202590358409</v>
+        <v>10.18013395536764</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B97" t="n">
-        <v>21976</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>Spontaneous</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>4.608176226510968</v>
+        <v>2.968933156507309</v>
       </c>
       <c r="E97" t="n">
-        <v>23531.91614294722</v>
+        <v>69444.47043386118</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>9.99770622777511</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B98" t="n">
-        <v>23243</v>
+        <v>53988</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>Spontaneous</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>4.608176226510968</v>
+        <v>2.968933156507309</v>
       </c>
       <c r="E98" t="n">
-        <v>23531.91614294722</v>
+        <v>69444.47043386118</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>10.05375929041443</v>
+        <v>10.89651707862917</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B99" t="n">
-        <v>21561</v>
+        <v>47586</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>Spontaneous</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>4.608176226510968</v>
+        <v>2.968933156507309</v>
       </c>
       <c r="E99" t="n">
-        <v>23531.91614294722</v>
+        <v>69444.47043386118</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>9.978641406136552</v>
+        <v>10.77029387931137</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B100" t="n">
-        <v>21740</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>Spontaneous</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4.608176226510968</v>
+        <v>2.968933156507309</v>
       </c>
       <c r="E100" t="n">
-        <v>23531.91614294722</v>
+        <v>69444.47043386118</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>9.9869091606752</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B101" t="n">
-        <v>18463</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>Spontaneous</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4.608176226510968</v>
+        <v>2.968933156507309</v>
       </c>
       <c r="E101" t="n">
-        <v>23531.91614294722</v>
+        <v>69444.47043386118</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>9.823524008395744</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B102" t="n">
-        <v>26374</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2982,15 +2982,15 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>10.18013395536764</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B103" t="n">
-        <v>61984.34968887378</v>
+        <v>46438</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -3007,15 +3007,15 @@
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>11.03463720778983</v>
+        <v>10.74587336856231</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B104" t="n">
-        <v>53988</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -3032,15 +3032,15 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>10.89651707862917</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B105" t="n">
-        <v>47586</v>
+        <v>48751</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -3057,15 +3057,15 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>10.77029387931137</v>
+        <v>10.79448098903612</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B106" t="n">
-        <v>61984.34968887378</v>
+        <v>26374</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -3082,12 +3082,12 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>11.03463720778983</v>
+        <v>10.18013395536764</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B107" t="n">
         <v>61984.34968887378</v>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B108" t="n">
-        <v>61984.34968887378</v>
+        <v>53988</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -3132,15 +3132,15 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>11.03463720778983</v>
+        <v>10.89651707862917</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B109" t="n">
-        <v>46438</v>
+        <v>47586</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -3157,12 +3157,12 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>10.74587336856231</v>
+        <v>10.77029387931137</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B110" t="n">
         <v>61984.34968887378</v>
@@ -3187,10 +3187,10 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B111" t="n">
-        <v>48751</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -3207,15 +3207,15 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>10.79448098903612</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B112" t="n">
-        <v>26374</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -3232,15 +3232,15 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>10.18013395536764</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B113" t="n">
-        <v>61984.34968887378</v>
+        <v>46438</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -3257,15 +3257,15 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>11.03463720778983</v>
+        <v>10.74587336856231</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B114" t="n">
-        <v>53988</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -3282,15 +3282,15 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>10.89651707862917</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B115" t="n">
-        <v>47586</v>
+        <v>48751</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -3307,15 +3307,15 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>10.77029387931137</v>
+        <v>10.79448098903612</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B116" t="n">
-        <v>61984.34968887378</v>
+        <v>26374</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -3332,12 +3332,12 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>11.03463720778983</v>
+        <v>10.18013395536764</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B117" t="n">
         <v>61984.34968887378</v>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B118" t="n">
-        <v>61984.34968887378</v>
+        <v>53988</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -3382,15 +3382,15 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>11.03463720778983</v>
+        <v>10.89651707862917</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B119" t="n">
-        <v>46438</v>
+        <v>47586</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -3407,12 +3407,12 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>10.74587336856231</v>
+        <v>10.77029387931137</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B120" t="n">
         <v>61984.34968887378</v>
@@ -3437,10 +3437,10 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B121" t="n">
-        <v>48751</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -3457,15 +3457,15 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>10.79448098903612</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B122" t="n">
-        <v>26374</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -3482,15 +3482,15 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>10.18013395536764</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B123" t="n">
-        <v>61984.34968887378</v>
+        <v>46438</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -3507,15 +3507,15 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>11.03463720778983</v>
+        <v>10.74587336856231</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B124" t="n">
-        <v>53988</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -3532,15 +3532,15 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>10.89651707862917</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B125" t="n">
-        <v>47586</v>
+        <v>48751</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -3557,15 +3557,15 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>10.77029387931137</v>
+        <v>10.79448098903612</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B126" t="n">
-        <v>61984.34968887378</v>
+        <v>38091</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -3582,12 +3582,12 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>11.03463720778983</v>
+        <v>10.5477333127379</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B127" t="n">
         <v>61984.34968887378</v>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B128" t="n">
-        <v>61984.34968887378</v>
+        <v>52209</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -3632,15 +3632,15 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>11.03463720778983</v>
+        <v>10.86301017280228</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B129" t="n">
-        <v>46438</v>
+        <v>29675</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -3657,12 +3657,12 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>10.74587336856231</v>
+        <v>10.29806021947787</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B130" t="n">
         <v>61984.34968887378</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B131" t="n">
-        <v>48751</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -3707,15 +3707,15 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>10.79448098903612</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B132" t="n">
-        <v>38091</v>
+        <v>56673</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -3732,15 +3732,15 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>10.5477333127379</v>
+        <v>10.94505318582496</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B133" t="n">
-        <v>61984.34968887378</v>
+        <v>50545</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -3757,15 +3757,15 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>11.03463720778983</v>
+        <v>10.83061930758816</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B134" t="n">
-        <v>52209</v>
+        <v>26966</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3782,15 +3782,15 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>10.86301017280228</v>
+        <v>10.20233209219402</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B135" t="n">
-        <v>29675</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3807,12 +3807,12 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>10.29806021947787</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B136" t="n">
         <v>61984.34968887378</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B137" t="n">
-        <v>61984.34968887378</v>
+        <v>67038</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3857,15 +3857,15 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>11.03463720778983</v>
+        <v>11.11301490177539</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B138" t="n">
-        <v>56673</v>
+        <v>22416</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3882,15 +3882,15 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>10.94505318582496</v>
+        <v>10.01753026857679</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B139" t="n">
-        <v>50545</v>
+        <v>20177</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -3907,15 +3907,15 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>10.83061930758816</v>
+        <v>9.912298620814678</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B140" t="n">
-        <v>26966</v>
+        <v>49079</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3932,15 +3932,15 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>10.20233209219402</v>
+        <v>10.80118652371915</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B141" t="n">
-        <v>61984.34968887378</v>
+        <v>53715</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3957,15 +3957,15 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>11.03463720778983</v>
+        <v>10.89144757110064</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B142" t="n">
-        <v>61984.34968887378</v>
+        <v>25876</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3982,15 +3982,15 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>11.03463720778983</v>
+        <v>10.16107117716388</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B143" t="n">
-        <v>67038</v>
+        <v>20972</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -4007,15 +4007,15 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>11.11301490177539</v>
+        <v>9.950943493692423</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B144" t="n">
-        <v>22416</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -4032,15 +4032,15 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>10.01753026857679</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B145" t="n">
-        <v>20177</v>
+        <v>37552</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -4057,15 +4057,15 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>9.912298620814678</v>
+        <v>10.53348191809081</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B146" t="n">
-        <v>49079</v>
+        <v>28495</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -4082,15 +4082,15 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>10.80118652371915</v>
+        <v>10.2574839122691</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B147" t="n">
-        <v>53715</v>
+        <v>35100</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -4107,15 +4107,15 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>10.89144757110064</v>
+        <v>10.46595640945396</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B148" t="n">
-        <v>25876</v>
+        <v>28420</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -4132,15 +4132,15 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>10.16107117716388</v>
+        <v>10.25484840165109</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B149" t="n">
-        <v>20972</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -4157,12 +4157,12 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>9.950943493692423</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B150" t="n">
         <v>61984.34968887378</v>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B151" t="n">
-        <v>37552</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -4207,15 +4207,15 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>10.53348191809081</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B152" t="n">
-        <v>28495</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -4232,15 +4232,15 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>10.2574839122691</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B153" t="n">
-        <v>35100</v>
+        <v>38714</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -4257,15 +4257,15 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>10.46595640945396</v>
+        <v>10.56395657070549</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B154" t="n">
-        <v>28420</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -4282,15 +4282,15 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>10.25484840165109</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B155" t="n">
-        <v>61984.34968887378</v>
+        <v>84518</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -4307,12 +4307,12 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>11.03463720778983</v>
+        <v>11.34471980841169</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B156" t="n">
         <v>61984.34968887378</v>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B157" t="n">
-        <v>61984.34968887378</v>
+        <v>73480</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -4357,15 +4357,15 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>11.03463720778983</v>
+        <v>11.20476853932906</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B158" t="n">
-        <v>61984.34968887378</v>
+        <v>52707</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -4382,15 +4382,15 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>11.03463720778983</v>
+        <v>10.87250355303316</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B159" t="n">
-        <v>38714</v>
+        <v>47221</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -4407,15 +4407,15 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>10.56395657070549</v>
+        <v>10.76259398788244</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B160" t="n">
-        <v>61984.34968887378</v>
+        <v>72861</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -4432,15 +4432,15 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>11.03463720778983</v>
+        <v>11.19630879542033</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B161" t="n">
-        <v>84518</v>
+        <v>26120</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -4457,15 +4457,15 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>11.34471980841169</v>
+        <v>10.17045658339037</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B162" t="n">
-        <v>61984.34968887378</v>
+        <v>75130</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -4482,15 +4482,15 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>11.03463720778983</v>
+        <v>11.22697522536321</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B163" t="n">
-        <v>73480</v>
+        <v>83591</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -4507,15 +4507,15 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>11.20476853932906</v>
+        <v>11.33369113777513</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B164" t="n">
-        <v>52707</v>
+        <v>20854</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -4532,15 +4532,15 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>10.87250355303316</v>
+        <v>9.945301055349539</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B165" t="n">
-        <v>47221</v>
+        <v>43004</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -4557,15 +4557,15 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>10.76259398788244</v>
+        <v>10.66904841360512</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B166" t="n">
-        <v>72861</v>
+        <v>26374</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -4582,15 +4582,15 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>11.19630879542033</v>
+        <v>10.18013395536764</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B167" t="n">
-        <v>26120</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -4607,15 +4607,15 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>10.17045658339037</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B168" t="n">
-        <v>75130</v>
+        <v>53988</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -4632,15 +4632,15 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>11.22697522536321</v>
+        <v>10.89651707862917</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B169" t="n">
-        <v>83591</v>
+        <v>47586</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -4657,15 +4657,15 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>11.33369113777513</v>
+        <v>10.77029387931137</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B170" t="n">
-        <v>20854</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -4682,15 +4682,15 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>9.945301055349539</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B171" t="n">
-        <v>43004</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -4707,15 +4707,15 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>10.66904841360512</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B172" t="n">
-        <v>26374</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -4732,15 +4732,15 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>10.18013395536764</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B173" t="n">
-        <v>61984.34968887378</v>
+        <v>46438</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -4757,15 +4757,15 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>11.03463720778983</v>
+        <v>10.74587336856231</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B174" t="n">
-        <v>53988</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -4782,15 +4782,15 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>10.89651707862917</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B175" t="n">
-        <v>47586</v>
+        <v>48751</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -4807,15 +4807,15 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>10.77029387931137</v>
+        <v>10.79448098903612</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B176" t="n">
-        <v>61984.34968887378</v>
+        <v>38091</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -4832,12 +4832,12 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>11.03463720778983</v>
+        <v>10.5477333127379</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B177" t="n">
         <v>61984.34968887378</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B178" t="n">
-        <v>61984.34968887378</v>
+        <v>52209</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -4882,15 +4882,15 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>11.03463720778983</v>
+        <v>10.86301017280228</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B179" t="n">
-        <v>46438</v>
+        <v>29675</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -4907,12 +4907,12 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>10.74587336856231</v>
+        <v>10.29806021947787</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B180" t="n">
         <v>61984.34968887378</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B181" t="n">
-        <v>48751</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -4957,15 +4957,15 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>10.79448098903612</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B182" t="n">
-        <v>38091</v>
+        <v>56673</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -4982,15 +4982,15 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>10.5477333127379</v>
+        <v>10.94505318582496</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B183" t="n">
-        <v>61984.34968887378</v>
+        <v>50545</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -5007,15 +5007,15 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>11.03463720778983</v>
+        <v>10.83061930758816</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B184" t="n">
-        <v>52209</v>
+        <v>26966</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -5032,15 +5032,15 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>10.86301017280228</v>
+        <v>10.20233209219402</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B185" t="n">
-        <v>29675</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -5057,15 +5057,15 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>10.29806021947787</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B186" t="n">
-        <v>61984.34968887378</v>
+        <v>26374</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -5082,12 +5082,12 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>11.03463720778983</v>
+        <v>10.18013395536764</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B187" t="n">
         <v>61984.34968887378</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B188" t="n">
-        <v>56673</v>
+        <v>53988</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -5132,15 +5132,15 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>10.94505318582496</v>
+        <v>10.89651707862917</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B189" t="n">
-        <v>50545</v>
+        <v>47586</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -5157,15 +5157,15 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>10.83061930758816</v>
+        <v>10.77029387931137</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B190" t="n">
-        <v>26966</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -5182,12 +5182,12 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>10.20233209219402</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B191" t="n">
         <v>61984.34968887378</v>
@@ -5212,10 +5212,10 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B192" t="n">
-        <v>26374</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -5232,15 +5232,15 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>10.18013395536764</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B193" t="n">
-        <v>61984.34968887378</v>
+        <v>46438</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -5257,15 +5257,15 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>11.03463720778983</v>
+        <v>10.74587336856231</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B194" t="n">
-        <v>53988</v>
+        <v>61984.34968887378</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -5282,15 +5282,15 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>10.89651707862917</v>
+        <v>11.03463720778983</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B195" t="n">
-        <v>47586</v>
+        <v>48751</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -5307,156 +5307,6 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>10.77029387931137</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="1" t="n">
-        <v>194</v>
-      </c>
-      <c r="B196" t="n">
-        <v>61984.34968887378</v>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Spontaneous</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>2.968933156507309</v>
-      </c>
-      <c r="E196" t="n">
-        <v>69444.47043386118</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>11.03463720778983</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="n">
-        <v>195</v>
-      </c>
-      <c r="B197" t="n">
-        <v>61984.34968887378</v>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Spontaneous</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>2.968933156507309</v>
-      </c>
-      <c r="E197" t="n">
-        <v>69444.47043386118</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>11.03463720778983</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="n">
-        <v>196</v>
-      </c>
-      <c r="B198" t="n">
-        <v>61984.34968887378</v>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Spontaneous</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>2.968933156507309</v>
-      </c>
-      <c r="E198" t="n">
-        <v>69444.47043386118</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="n">
-        <v>11.03463720778983</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="n">
-        <v>197</v>
-      </c>
-      <c r="B199" t="n">
-        <v>46438</v>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Spontaneous</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>2.968933156507309</v>
-      </c>
-      <c r="E199" t="n">
-        <v>69444.47043386118</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
-        <v>10.74587336856231</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="1" t="n">
-        <v>198</v>
-      </c>
-      <c r="B200" t="n">
-        <v>61984.34968887378</v>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Spontaneous</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>2.968933156507309</v>
-      </c>
-      <c r="E200" t="n">
-        <v>69444.47043386118</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="n">
-        <v>11.03463720778983</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="n">
-        <v>199</v>
-      </c>
-      <c r="B201" t="n">
-        <v>48751</v>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Spontaneous</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>2.968933156507309</v>
-      </c>
-      <c r="E201" t="n">
-        <v>69444.47043386118</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" t="n">
         <v>10.79448098903612</v>
       </c>
     </row>
